--- a/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_TD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BD002F3-8DA3-40A4-A6DB-A8B69A3A60A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A75DB609-15E4-4ECC-86E5-CF953906F169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="495" windowWidth="18900" windowHeight="11100" xr2:uid="{A13C03FF-C1B2-4233-AE84-566ECA6C31CD}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{16D9531F-C87B-4EF7-8743-587CE65C5181}"/>
   </bookViews>
   <sheets>
     <sheet name="05_LTAN06_800km_1213COLD_PX_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{641B8761-ABB8-4213-9921-48C5A841C01B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B5AAEA-17E3-4095-9A97-F3AB417DED08}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A75DB609-15E4-4ECC-86E5-CF953906F169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B859EF9-F537-4B61-90BD-0EC5B208A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{16D9531F-C87B-4EF7-8743-587CE65C5181}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{EE52E21B-A396-4C00-9470-822F21015A3E}"/>
   </bookViews>
   <sheets>
     <sheet name="05_LTAN06_800km_1213COLD_PX_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B5AAEA-17E3-4095-9A97-F3AB417DED08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBB3657-3908-4B73-9BD5-66990CB14142}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>50.125729999999997</v>
+        <v>50.172629999999998</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>50.125729999999997</v>
+        <v>50.172629999999998</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>50.372540000000001</v>
+        <v>50.417949999999998</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>50.592199999999998</v>
+        <v>50.637549999999997</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>50.792659999999998</v>
+        <v>50.838880000000003</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>50.979579999999999</v>
+        <v>51.026420000000002</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>51.156219999999998</v>
+        <v>51.203209999999999</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>51.324550000000002</v>
+        <v>51.371360000000003</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>51.486539999999998</v>
+        <v>51.532640000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>51.643259999999998</v>
+        <v>51.688319999999997</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>51.795319999999997</v>
+        <v>51.839399999999998</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>51.942799999999998</v>
+        <v>51.987130000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>52.086480000000002</v>
+        <v>52.131680000000003</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>52.227170000000001</v>
+        <v>52.273380000000003</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>52.365470000000002</v>
+        <v>52.412509999999997</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>52.501309999999997</v>
+        <v>52.549059999999997</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>52.634329999999999</v>
+        <v>52.68235</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>52.764470000000003</v>
+        <v>52.812280000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>52.891959999999997</v>
+        <v>52.939279999999997</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>51.46949</v>
+        <v>51.524839999999998</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>50.227400000000003</v>
+        <v>50.287460000000003</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>49.112520000000004</v>
+        <v>49.175159999999998</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>48.092210000000001</v>
+        <v>48.154640000000001</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>47.146299999999997</v>
+        <v>47.20673</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>46.260820000000002</v>
+        <v>46.318210000000001</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>45.4253</v>
+        <v>45.479410000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>44.632910000000003</v>
+        <v>44.683639999999997</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>43.878070000000001</v>
+        <v>43.925870000000003</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>43.156320000000001</v>
+        <v>43.201889999999999</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>42.464280000000002</v>
+        <v>42.508069999999996</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>41.797649999999997</v>
+        <v>41.839669999999998</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>41.153889999999997</v>
+        <v>41.194290000000002</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>40.531489999999998</v>
+        <v>40.570569999999996</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>39.92953</v>
+        <v>39.968400000000003</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>39.346600000000002</v>
+        <v>39.385640000000002</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>38.781640000000003</v>
+        <v>38.820120000000003</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>39.780259999999998</v>
+        <v>39.810040000000001</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>40.614170000000001</v>
+        <v>40.639470000000003</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>41.334440000000001</v>
+        <v>41.357419999999998</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>41.97157</v>
+        <v>41.993319999999997</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>42.545140000000004</v>
+        <v>42.566130000000001</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>43.067079999999997</v>
+        <v>43.088180000000001</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>43.545920000000002</v>
+        <v>43.56814</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>43.988390000000003</v>
+        <v>44.012459999999997</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>44.400910000000003</v>
+        <v>44.426079999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>44.786999999999999</v>
+        <v>44.81259</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>45.149239999999999</v>
+        <v>45.17492</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>45.489310000000003</v>
+        <v>45.516710000000003</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>45.809420000000003</v>
+        <v>45.839500000000001</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>46.111750000000001</v>
+        <v>46.14452</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>46.398710000000001</v>
+        <v>46.432780000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>46.67145</v>
+        <v>46.705829999999999</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>46.930790000000002</v>
+        <v>46.965420000000002</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>47.177439999999997</v>
+        <v>47.212980000000002</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>47.412140000000001</v>
+        <v>47.449129999999997</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>47.635390000000001</v>
+        <v>47.673960000000001</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>47.847940000000001</v>
+        <v>47.888089999999998</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>48.050539999999998</v>
+        <v>48.09225</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>48.244289999999999</v>
+        <v>48.286920000000002</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>48.429400000000001</v>
+        <v>48.472450000000002</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>48.606090000000002</v>
+        <v>48.649250000000002</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>48.774209999999997</v>
+        <v>48.817959999999999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>48.93441</v>
+        <v>48.979019999999998</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>49.087319999999998</v>
+        <v>49.132980000000003</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>49.233519999999999</v>
+        <v>49.280320000000003</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>49.373240000000003</v>
+        <v>49.421259999999997</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>49.507190000000001</v>
+        <v>49.555950000000003</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>49.635829999999999</v>
+        <v>49.684750000000001</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>49.759279999999997</v>
+        <v>49.808039999999998</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>49.87791</v>
+        <v>49.926589999999997</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>49.992080000000001</v>
+        <v>50.04063</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>50.102069999999998</v>
+        <v>50.150399999999998</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>50.20879</v>
+        <v>50.257069999999999</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>50.312069999999999</v>
+        <v>50.360509999999998</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>50.412039999999998</v>
+        <v>50.460769999999997</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>50.50909</v>
+        <v>50.558019999999999</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>50.603389999999997</v>
+        <v>50.652349999999998</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>50.695439999999998</v>
+        <v>50.744300000000003</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>50.785629999999998</v>
+        <v>50.834350000000001</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>50.873869999999997</v>
+        <v>50.922580000000004</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>50.960520000000002</v>
+        <v>51.009349999999998</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>51.045780000000001</v>
+        <v>51.094790000000003</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>51.129710000000003</v>
+        <v>51.178890000000003</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>51.213149999999999</v>
+        <v>51.262560000000001</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>51.295999999999999</v>
+        <v>51.345739999999999</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>51.378259999999997</v>
+        <v>51.42839</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>51.460270000000001</v>
+        <v>51.510559999999998</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>51.542009999999998</v>
+        <v>51.59225</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>51.62341</v>
+        <v>51.673729999999999</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>51.704369999999997</v>
+        <v>51.755420000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>51.784970000000001</v>
+        <v>51.837229999999998</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>51.865839999999999</v>
+        <v>51.919060000000002</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>51.947240000000001</v>
+        <v>52.000810000000001</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>52.02899</v>
+        <v>52.082410000000003</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>52.11121</v>
+        <v>52.164099999999998</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>52.193730000000002</v>
+        <v>52.246000000000002</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>52.27637</v>
+        <v>52.328110000000002</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>52.358759999999997</v>
+        <v>52.41046</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>52.440919999999998</v>
+        <v>52.492829999999998</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>52.522660000000002</v>
+        <v>52.574840000000002</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>52.6036</v>
+        <v>52.65578</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>52.683929999999997</v>
+        <v>52.735860000000002</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>52.763669999999998</v>
+        <v>52.815629999999999</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>52.842750000000002</v>
+        <v>52.895429999999998</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>52.921059999999997</v>
+        <v>52.97495</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>52.999429999999997</v>
+        <v>53.053980000000003</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>53.078040000000001</v>
+        <v>53.132579999999997</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>53.156750000000002</v>
+        <v>53.210850000000001</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>53.2361</v>
+        <v>53.289149999999999</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>53.316090000000003</v>
+        <v>53.367730000000002</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>53.396529999999998</v>
+        <v>53.446820000000002</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>53.476889999999997</v>
+        <v>53.52704</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>53.55744</v>
+        <v>53.608089999999997</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>53.638590000000001</v>
+        <v>53.689909999999998</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>53.72063</v>
+        <v>53.772440000000003</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>53.803190000000001</v>
+        <v>53.855400000000003</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>53.885680000000001</v>
+        <v>53.93788</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>53.967840000000002</v>
+        <v>54.019559999999998</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>54.049720000000001</v>
+        <v>54.100709999999999</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>52.584049999999998</v>
+        <v>52.642850000000003</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>51.301189999999998</v>
+        <v>51.364490000000004</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>50.14781</v>
+        <v>50.213500000000003</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>49.09093</v>
+        <v>49.156239999999997</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>48.110329999999998</v>
+        <v>48.173470000000002</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>47.19191</v>
+        <v>47.251869999999997</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>46.325069999999997</v>
+        <v>46.381619999999998</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>45.502879999999998</v>
+        <v>45.555929999999996</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>44.719679999999997</v>
+        <v>44.769680000000001</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>43.970910000000003</v>
+        <v>44.01858</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>43.253100000000003</v>
+        <v>43.298900000000003</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>42.561889999999998</v>
+        <v>42.605829999999997</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>41.894669999999998</v>
+        <v>41.936909999999997</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>41.249870000000001</v>
+        <v>41.29072</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>40.626510000000003</v>
+        <v>40.667070000000002</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>40.023110000000003</v>
+        <v>40.063789999999997</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>39.438580000000002</v>
+        <v>39.478630000000003</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>40.418370000000003</v>
+        <v>40.449669999999998</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>41.234070000000003</v>
+        <v>41.260829999999999</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>41.936750000000004</v>
+        <v>41.96114</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>42.556910000000002</v>
+        <v>42.580010000000001</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>43.114100000000001</v>
+        <v>43.136409999999998</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>43.620240000000003</v>
+        <v>43.642620000000001</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>44.083849999999998</v>
+        <v>44.107309999999998</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>44.51164</v>
+        <v>44.536909999999999</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>44.91</v>
+        <v>44.936329999999998</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>45.282449999999997</v>
+        <v>45.309159999999999</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>45.631540000000001</v>
+        <v>45.658299999999997</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>45.958919999999999</v>
+        <v>45.987369999999999</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>46.26681</v>
+        <v>46.297899999999998</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>46.557340000000003</v>
+        <v>46.59111</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>46.832940000000001</v>
+        <v>46.86797</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>47.094729999999998</v>
+        <v>47.130029999999998</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>47.343510000000002</v>
+        <v>47.379040000000003</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>47.579970000000003</v>
+        <v>47.616379999999999</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>47.804850000000002</v>
+        <v>47.842680000000001</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>48.018619999999999</v>
+        <v>48.058019999999999</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>48.222029999999997</v>
+        <v>48.262990000000002</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>48.41583</v>
+        <v>48.458320000000001</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>48.601080000000003</v>
+        <v>48.644480000000001</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>48.777999999999999</v>
+        <v>48.821779999999997</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>48.946779999999997</v>
+        <v>48.990659999999998</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>49.10727</v>
+        <v>49.151719999999997</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>49.260109999999997</v>
+        <v>49.305410000000002</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>49.405920000000002</v>
+        <v>49.452240000000003</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>49.545270000000002</v>
+        <v>49.59272</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>49.678370000000001</v>
+        <v>49.727020000000003</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>49.805929999999996</v>
+        <v>49.855310000000003</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>49.928400000000003</v>
+        <v>49.977930000000001</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>50.045900000000003</v>
+        <v>50.095260000000003</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>50.158790000000003</v>
+        <v>50.208030000000001</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>50.267400000000002</v>
+        <v>50.316510000000001</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>50.372030000000002</v>
+        <v>50.420900000000003</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>50.473559999999999</v>
+        <v>50.522379999999998</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>50.571829999999999</v>
+        <v>50.620800000000003</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>50.666960000000003</v>
+        <v>50.716209999999997</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>50.759329999999999</v>
+        <v>50.808759999999999</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>50.8491</v>
+        <v>50.898560000000003</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>50.936779999999999</v>
+        <v>50.98612</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>51.022730000000003</v>
+        <v>51.071930000000002</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>51.10689</v>
+        <v>51.15605</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>51.189570000000003</v>
+        <v>51.238849999999999</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>51.270989999999998</v>
+        <v>51.320450000000001</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>51.351210000000002</v>
+        <v>51.400820000000003</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>51.431060000000002</v>
+        <v>51.480890000000002</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>51.510429999999999</v>
+        <v>51.560580000000002</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>51.589309999999998</v>
+        <v>51.63984</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>51.668050000000001</v>
+        <v>51.718739999999997</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>51.74662</v>
+        <v>51.797249999999998</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>51.824939999999998</v>
+        <v>51.87565</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>51.902929999999998</v>
+        <v>51.954349999999998</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>51.980640000000001</v>
+        <v>52.033259999999999</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>52.058700000000002</v>
+        <v>52.112279999999998</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>52.13738</v>
+        <v>52.191310000000001</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>52.21649</v>
+        <v>52.27026</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>52.296140000000001</v>
+        <v>52.349379999999996</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>52.376159999999999</v>
+        <v>52.42877</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>52.456380000000003</v>
+        <v>52.508450000000003</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>52.53642</v>
+        <v>52.588439999999999</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>52.616289999999999</v>
+        <v>52.668520000000001</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>52.695799999999998</v>
+        <v>52.748289999999997</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>52.77458</v>
+        <v>52.827069999999999</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>52.852789999999999</v>
+        <v>52.90502</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>52.930480000000003</v>
+        <v>52.98274</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>53.007559999999998</v>
+        <v>53.060540000000003</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>53.083930000000002</v>
+        <v>53.138109999999998</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>53.160409999999999</v>
+        <v>53.215240000000001</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>53.237160000000003</v>
+        <v>53.291980000000002</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>53.314079999999997</v>
+        <v>53.368450000000003</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>53.391669999999998</v>
+        <v>53.444989999999997</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>53.469949999999997</v>
+        <v>53.521850000000001</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>53.548720000000003</v>
+        <v>53.599260000000001</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>53.62744</v>
+        <v>53.677849999999999</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>53.706409999999998</v>
+        <v>53.757309999999997</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>53.786009999999997</v>
+        <v>53.837569999999999</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>53.866520000000001</v>
+        <v>53.918570000000003</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>53.947600000000001</v>
+        <v>54.000050000000002</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>54.028640000000003</v>
+        <v>54.081069999999997</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>54.109380000000002</v>
+        <v>54.16133</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>54.189880000000002</v>
+        <v>54.24109</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>52.722880000000004</v>
+        <v>52.7819</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>51.438769999999998</v>
+        <v>51.502279999999999</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>50.284179999999999</v>
+        <v>50.350090000000002</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>49.22616</v>
+        <v>49.291670000000003</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>48.244450000000001</v>
+        <v>48.307810000000003</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>47.32497</v>
+        <v>47.38514</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>46.45711</v>
+        <v>46.513860000000001</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>45.633929999999999</v>
+        <v>45.687179999999998</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>44.849769999999999</v>
+        <v>44.899979999999999</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>44.100070000000002</v>
+        <v>44.147939999999998</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>43.381369999999997</v>
+        <v>43.42736</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>42.68929</v>
+        <v>42.733420000000002</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>42.021230000000003</v>
+        <v>42.063650000000003</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>41.375599999999999</v>
+        <v>41.416629999999998</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>40.751429999999999</v>
+        <v>40.792180000000002</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>40.147260000000003</v>
+        <v>40.188119999999998</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>39.561959999999999</v>
+        <v>39.602200000000003</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>40.540990000000001</v>
+        <v>40.572470000000003</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>41.355910000000002</v>
+        <v>41.382849999999998</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>42.0578</v>
+        <v>42.082369999999997</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>42.677160000000001</v>
+        <v>42.70044</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>43.233550000000001</v>
+        <v>43.256039999999999</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>43.738900000000001</v>
+        <v>43.76144</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>44.201709999999999</v>
+        <v>44.22533</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>44.628709999999998</v>
+        <v>44.654139999999998</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>45.026269999999997</v>
+        <v>45.052770000000002</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>45.397930000000002</v>
+        <v>45.424799999999998</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>45.74624</v>
+        <v>45.773159999999997</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>46.072839999999999</v>
+        <v>46.10145</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>46.379950000000001</v>
+        <v>46.411200000000001</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>46.669719999999998</v>
+        <v>46.70364</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>46.94455</v>
+        <v>46.97974</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>47.205579999999998</v>
+        <v>47.241039999999998</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>47.453609999999998</v>
+        <v>47.489289999999997</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>47.689329999999998</v>
+        <v>47.725900000000003</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>47.913469999999997</v>
+        <v>47.951459999999997</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>48.126519999999999</v>
+        <v>48.166069999999998</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>48.329210000000003</v>
+        <v>48.370310000000003</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>48.522289999999998</v>
+        <v>48.564920000000001</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>48.706829999999997</v>
+        <v>48.750360000000001</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>48.883040000000001</v>
+        <v>48.926969999999997</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>49.051130000000001</v>
+        <v>49.095149999999997</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>49.210940000000001</v>
+        <v>49.255519999999997</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>49.363100000000003</v>
+        <v>49.408529999999999</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>49.508240000000001</v>
+        <v>49.554690000000001</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>49.646920000000001</v>
+        <v>49.694499999999998</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>49.779359999999997</v>
+        <v>49.828139999999998</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>49.906269999999999</v>
+        <v>49.955779999999997</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>50.028100000000002</v>
+        <v>50.077750000000002</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>50.144959999999998</v>
+        <v>50.19444</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>50.257219999999997</v>
+        <v>50.30659</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>50.365209999999998</v>
+        <v>50.414439999999999</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>50.46922</v>
+        <v>50.518210000000003</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>50.570149999999998</v>
+        <v>50.619079999999997</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>50.667819999999999</v>
+        <v>50.716900000000003</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>50.762349999999998</v>
+        <v>50.811709999999998</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>50.854129999999998</v>
+        <v>50.903680000000001</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>50.943330000000003</v>
+        <v>50.992890000000003</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>51.030430000000003</v>
+        <v>51.07987</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>51.115810000000003</v>
+        <v>51.165109999999999</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>51.199399999999997</v>
+        <v>51.248669999999997</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>51.281529999999997</v>
+        <v>51.330919999999999</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>51.362400000000001</v>
+        <v>51.411960000000001</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>51.442070000000001</v>
+        <v>51.491779999999999</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>51.521380000000001</v>
+        <v>51.571309999999997</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>51.60022</v>
+        <v>51.650469999999999</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>51.678570000000001</v>
+        <v>51.729199999999999</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>51.756790000000002</v>
+        <v>51.807569999999998</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>51.83484</v>
+        <v>51.885570000000001</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>51.912649999999999</v>
+        <v>51.963459999999998</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>51.990130000000001</v>
+        <v>52.041649999999997</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>52.067329999999998</v>
+        <v>52.120049999999999</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>52.1449</v>
+        <v>52.198569999999997</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>52.223080000000003</v>
+        <v>52.27711</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>52.301699999999997</v>
+        <v>52.355559999999997</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>52.380870000000002</v>
+        <v>52.434199999999997</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>52.460410000000003</v>
+        <v>52.513109999999998</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>52.540149999999997</v>
+        <v>52.592309999999998</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>52.619720000000001</v>
+        <v>52.671819999999997</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>52.699120000000001</v>
+        <v>52.751429999999999</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>52.778170000000003</v>
+        <v>52.830739999999999</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>52.856479999999998</v>
+        <v>52.909050000000001</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>52.934240000000003</v>
+        <v>52.986559999999997</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B859EF9-F537-4B61-90BD-0EC5B208A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16390987-67B2-4F3D-9A6C-682919FF6A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{EE52E21B-A396-4C00-9470-822F21015A3E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6F86FA97-9948-41DC-AA7D-D93AB943D5C5}"/>
   </bookViews>
   <sheets>
     <sheet name="05_LTAN06_800km_1213COLD_PX_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBB3657-3908-4B73-9BD5-66990CB14142}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F963704-5F8C-44FC-A1D6-E312CE52FE1F}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16390987-67B2-4F3D-9A6C-682919FF6A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C153288A-8EA3-4311-B9F4-015B0C1BC53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6F86FA97-9948-41DC-AA7D-D93AB943D5C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{333242E8-6403-4A5C-B24D-D65727BCD22E}"/>
   </bookViews>
   <sheets>
     <sheet name="05_LTAN06_800km_1213COLD_PX_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F963704-5F8C-44FC-A1D6-E312CE52FE1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE66A5CB-6E9B-4272-BAD5-D91DA07D8DF3}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
